--- a/data/trans_bre/IP1003-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 5,54</t>
+          <t>-6,26; 5,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 7,54</t>
+          <t>-1,58; 7,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 2,22</t>
+          <t>-7,17; 1,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 4,89</t>
+          <t>-7,63; 5,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,41; 93,87</t>
+          <t>-52,72; 79,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 280,22</t>
+          <t>-26,35; 254,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-82,68; 87,28</t>
+          <t>-83,34; 87,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-61,42; 98,6</t>
+          <t>-60,74; 108,48</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 2,0</t>
+          <t>-5,73; 2,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,32; -1,27</t>
+          <t>-8,6; -1,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 2,26</t>
+          <t>-4,99; 2,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 3,21</t>
+          <t>-6,77; 2,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,69; 40,04</t>
+          <t>-59,13; 41,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,31; -15,05</t>
+          <t>-81,74; -22,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,92; 43,53</t>
+          <t>-55,28; 56,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,02; 49,64</t>
+          <t>-57,6; 41,08</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 2,52</t>
+          <t>-5,42; 2,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 3,39</t>
+          <t>-4,34; 3,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,16</t>
+          <t>-3,29; 3,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 1,07</t>
+          <t>-6,58; 1,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,9; 59,96</t>
+          <t>-68,0; 70,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-65,42; 105,63</t>
+          <t>-64,58; 104,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,27; 172,05</t>
+          <t>-62,51; 221,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-83,56; 45,12</t>
+          <t>-79,07; 51,03</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 3,24</t>
+          <t>-4,18; 3,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 2,68</t>
+          <t>-5,47; 2,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,24</t>
+          <t>-2,48; 4,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,41; -0,04</t>
+          <t>-9,25; 0,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,72; 84,1</t>
+          <t>-54,3; 92,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,19; 68,01</t>
+          <t>-65,53; 69,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 173,61</t>
+          <t>-46,43; 185,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,75; 13,17</t>
+          <t>-82,17; 11,92</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 1,07</t>
+          <t>-2,94; 1,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,58</t>
+          <t>-3,35; 0,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,31</t>
+          <t>-2,5; 1,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -0,28</t>
+          <t>-5,23; -0,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 18,26</t>
+          <t>-36,68; 19,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 13,7</t>
+          <t>-47,5; 12,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 31,24</t>
+          <t>-40,26; 27,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-53,72; -3,9</t>
+          <t>-54,49; -4,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 5,12</t>
+          <t>-5,79; 5,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 7,32</t>
+          <t>-1,4; 7,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 1,87</t>
+          <t>-7,08; 2,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 5,44</t>
+          <t>-8,57; 4,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,72; 79,46</t>
+          <t>-50,88; 84,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 254,37</t>
+          <t>-29,41; 297,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-83,34; 87,36</t>
+          <t>-81,11; 86,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,74; 108,48</t>
+          <t>-60,11; 87,22</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 2,07</t>
+          <t>-5,85; 1,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -1,63</t>
+          <t>-8,82; -1,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,78</t>
+          <t>-4,9; 2,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 2,82</t>
+          <t>-6,63; 2,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,13; 41,97</t>
+          <t>-59,66; 36,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,74; -22,76</t>
+          <t>-80,58; -19,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,28; 56,02</t>
+          <t>-57,1; 48,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,6; 41,08</t>
+          <t>-55,95; 45,24</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 2,64</t>
+          <t>-5,49; 3,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 3,43</t>
+          <t>-4,02; 3,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 3,74</t>
+          <t>-3,04; 3,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 1,22</t>
+          <t>-7,19; 1,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-68,0; 70,21</t>
+          <t>-62,83; 86,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,58; 104,65</t>
+          <t>-59,55; 123,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-62,51; 221,5</t>
+          <t>-64,24; 210,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-79,07; 51,03</t>
+          <t>-82,35; 42,94</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 3,52</t>
+          <t>-3,76; 3,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 2,38</t>
+          <t>-4,97; 2,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 4,8</t>
+          <t>-2,38; 4,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 0,25</t>
+          <t>-9,72; 0,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,3; 92,99</t>
+          <t>-52,06; 107,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,53; 69,64</t>
+          <t>-65,24; 58,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 185,98</t>
+          <t>-42,66; 188,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,17; 11,92</t>
+          <t>-82,01; 7,16</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,11</t>
+          <t>-3,01; 1,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,62</t>
+          <t>-3,45; 0,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,2</t>
+          <t>-2,52; 1,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -0,31</t>
+          <t>-5,46; -0,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 19,83</t>
+          <t>-37,86; 23,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 12,77</t>
+          <t>-46,73; 9,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 27,79</t>
+          <t>-40,02; 34,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,49; -4,34</t>
+          <t>-54,75; -2,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-1,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-11,09%</t>
+          <t>-11,23%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 5,02</t>
+          <t>-5,46; 5,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 7,94</t>
+          <t>-1,91; 7,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 2,41</t>
+          <t>-6,56; 2,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 4,83</t>
+          <t>-8,28; 5,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,88; 84,26</t>
+          <t>-49,41; 93,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 297,7</t>
+          <t>-35,18; 280,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-81,11; 86,87</t>
+          <t>-82,68; 87,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,11; 87,22</t>
+          <t>-60,0; 96,47</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,71</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-18,25%</t>
+          <t>-12,96%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 1,55</t>
+          <t>-5,52; 2,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,82; -1,61</t>
+          <t>-8,32; -1,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 2,55</t>
+          <t>-5,25; 2,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 2,93</t>
+          <t>-5,93; 3,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 36,07</t>
+          <t>-58,69; 40,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,58; -19,47</t>
+          <t>-81,31; -15,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,1; 48,82</t>
+          <t>-57,92; 43,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,95; 45,24</t>
+          <t>-50,35; 58,38</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-2,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-46,25%</t>
+          <t>-37,96%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 3,02</t>
+          <t>-5,21; 2,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 3,67</t>
+          <t>-4,37; 3,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 3,71</t>
+          <t>-3,45; 3,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 1,09</t>
+          <t>-7,76; 1,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 86,11</t>
+          <t>-64,9; 59,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 123,03</t>
+          <t>-65,42; 105,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-64,24; 210,17</t>
+          <t>-63,27; 172,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-82,35; 42,94</t>
+          <t>-78,49; 83,36</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,47</t>
+          <t>-4,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-53,26%</t>
+          <t>-49,81%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,64</t>
+          <t>-3,91; 3,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 2,2</t>
+          <t>-4,75; 2,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,51</t>
+          <t>-2,87; 4,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 0,07</t>
+          <t>-8,52; 0,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,06; 107,17</t>
+          <t>-54,72; 84,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 58,96</t>
+          <t>-63,19; 68,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 188,24</t>
+          <t>-50,96; 173,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,01; 7,16</t>
+          <t>-80,54; 15,04</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-2,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-33,09%</t>
+          <t>-27,34%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,37</t>
+          <t>-2,97; 1,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,43</t>
+          <t>-3,49; 0,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,37</t>
+          <t>-2,58; 1,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; -0,2</t>
+          <t>-4,96; 0,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 23,97</t>
+          <t>-38,7; 18,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 9,24</t>
+          <t>-46,85; 13,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 34,68</t>
+          <t>-42,83; 31,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,75; -2,51</t>
+          <t>-50,05; 3,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,71</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,36</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,07</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>59,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-40,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-11,23%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.2587153541740203</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.707997942386784</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.357590899856742</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.068418260515444</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.02933245370210149</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.5916842141670281</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.4002039561504657</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1122777548073476</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,46; 5,54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,91; 7,54</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,56; 2,22</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-8,28; 5,3</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-49,41; 93,87</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-35,18; 280,22</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-82,68; 87,28</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-60,0; 96,47</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.459184939230498</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.908059562996848</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.560871987503692</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.278451361980213</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4941427971845375</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3517553567467191</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.8268035750069069</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.5999611722295727</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.536435328563203</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.53656937536981</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.21597640476841</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.298125676712204</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.9387159957901801</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.802183199835981</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.8727581041005678</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.9646894699011034</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,87</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-4,86</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-24,97%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-59,99%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-20,15%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-12,96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,52; 2,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-8,32; -1,27</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,25; 2,26</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,93; 3,77</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-58,69; 40,04</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-81,31; -15,05</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-57,92; 43,53</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-50,35; 58,38</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.87131184257139</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-4.864018605096289</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.411555945775077</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.199721037385351</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2496962077466296</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.5998587107124743</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.2015042722318562</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1296488263607276</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,32</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,47</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-22,01%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-10,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-37,96%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.519545370555298</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-8.324606788277787</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.251940065574963</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.930629750188289</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.58693452940098</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8131494153426013</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5791901334907923</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5034664993781099</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,21; 2,52</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,37; 3,39</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,45; 3,16</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,76; 1,93</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-64,9; 59,96</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-65,42; 105,63</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-63,27; 172,05</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-78,49; 83,36</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.99804305531482</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-1.268218019809457</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.262040364046644</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.771649786605755</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.4004185381258563</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.1504735836155539</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.435284773164957</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.5837732296716479</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,37</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-4,04</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-2,87%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-23,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-49,81%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.317912600774743</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.5121236533704949</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1349359480493854</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.466122152148448</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2200598286721107</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1004533709051674</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.03818337355994288</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.3796476433760446</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,91; 3,24</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,75; 2,68</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,87; 4,24</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,52; 0,47</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-54,72; 84,1</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-63,19; 68,01</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-50,96; 173,61</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-80,54; 15,04</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.206574454183063</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.369537479536894</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.452381630625997</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.758297814380677</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6489910383852618</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.6542181125589739</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6326774149568635</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7849109590171853</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.519535361635811</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.391368523666928</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.156453850347678</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.926809889678833</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.5995809269594576</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.056301619067429</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.720489150920854</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.8336089684502132</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.1604904190462421</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.366044010717475</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8459162650561035</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-4.041534113301029</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.02874436441286294</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.23187332768292</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.2104395044748994</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.4981482401548269</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.908750541030476</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.74806927609737</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.869324950460582</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.524548104876505</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5471649434472318</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6318839934755698</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5096374815235746</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.8054430971063542</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.236203863171824</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.678287767617845</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.241742117214976</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.4688910226816749</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.8410444432319738</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.6800508701789411</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.736114381469622</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.1504053781984887</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-13,69%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-23,02%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-11,97%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-27,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,97; 1,07</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,49; 0,58</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,58; 1,31</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,96; 0,21</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-38,7; 18,26</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-46,85; 13,7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-42,83; 31,24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-50,05; 3,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.9464748344904045</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.405239041899653</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.6204013575452534</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-2.286393119065867</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1368949393426817</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.230207948989328</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1197161939461218</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.2734041732391645</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.97284247903847</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.494179811215464</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.576880149412136</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.957075127453722</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3869689790917459</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4684907827264612</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4282743232494939</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.5005083076296172</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.071252964359931</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5767018124861668</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.308614819353522</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.2107498514385048</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.1825511213538469</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1370033663594252</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.3124156392450821</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.03278702370073539</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
